--- a/pipeline/credit_rating/output/fiinratings_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/fiinratings_xhtn_20260918.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,77 +421,77 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ngay_cong_bo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>to_chuc_phat_hanh</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>linh_vuc</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>trang_thai_xep_hang</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>loai_y_kien</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ket_qua_xep_hang</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>trien_vong</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ma_trai_phieu</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>bao_cao_vi</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>bao_cao_en</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>link_to_chuc_phat_hanh</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>issuer_id</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>to_chuc_xhtn</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>thoi_gian_scrape</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ngay_cong_bo_dt</t>
         </is>
@@ -573,10 +561,10 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="n">
         <v>46261</v>
       </c>
     </row>
@@ -644,10 +632,10 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="n">
         <v>46258</v>
       </c>
     </row>
@@ -719,10 +707,10 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="n">
         <v>46251</v>
       </c>
     </row>
@@ -782,10 +770,10 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O5" s="1" t="n">
         <v>46224</v>
       </c>
     </row>
@@ -849,10 +837,10 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O6" s="1" t="n">
         <v>46223</v>
       </c>
     </row>
@@ -916,10 +904,10 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -983,10 +971,10 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O8" s="1" t="n">
         <v>46203</v>
       </c>
     </row>
@@ -1046,10 +1034,10 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O9" s="1" t="n">
         <v>46198</v>
       </c>
     </row>
@@ -1121,10 +1109,10 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O10" s="1" t="n">
         <v>46196</v>
       </c>
     </row>
@@ -1196,10 +1184,10 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O11" s="1" t="n">
         <v>46196</v>
       </c>
     </row>
@@ -1259,10 +1247,10 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O12" s="1" t="n">
         <v>46188</v>
       </c>
     </row>
@@ -1322,10 +1310,10 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O13" s="1" t="n">
         <v>46184</v>
       </c>
     </row>
@@ -1389,10 +1377,10 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O14" s="1" t="n">
         <v>46184</v>
       </c>
     </row>
@@ -1460,10 +1448,10 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O15" s="1" t="n">
         <v>46182</v>
       </c>
     </row>
@@ -1531,10 +1519,10 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O16" s="1" t="n">
         <v>46182</v>
       </c>
     </row>
@@ -1598,10 +1586,10 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O17" s="1" t="n">
         <v>46181</v>
       </c>
     </row>
@@ -1661,10 +1649,10 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O18" s="1" t="n">
         <v>46181</v>
       </c>
     </row>
@@ -1728,10 +1716,10 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O19" s="1" t="n">
         <v>46178</v>
       </c>
     </row>
@@ -1803,10 +1791,10 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O20" s="1" t="n">
         <v>46178</v>
       </c>
     </row>
@@ -1874,10 +1862,10 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O21" s="1" t="n">
         <v>46177</v>
       </c>
     </row>
@@ -1937,10 +1925,10 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O22" s="1" t="n">
         <v>46177</v>
       </c>
     </row>
@@ -2004,10 +1992,10 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O23" s="1" t="n">
         <v>46170</v>
       </c>
     </row>
@@ -2067,10 +2055,10 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O24" s="1" t="n">
         <v>46169</v>
       </c>
     </row>
@@ -2130,10 +2118,10 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O25" s="1" t="n">
         <v>46153</v>
       </c>
     </row>
@@ -2197,10 +2185,10 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O26" s="1" t="n">
         <v>46150</v>
       </c>
     </row>
@@ -2264,10 +2252,10 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O27" s="1" t="n">
         <v>46150</v>
       </c>
     </row>
@@ -2327,10 +2315,10 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O28" s="1" t="n">
         <v>46141</v>
       </c>
     </row>
@@ -2390,10 +2378,10 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O29" s="1" t="n">
         <v>46137</v>
       </c>
     </row>
@@ -2453,10 +2441,10 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O30" s="1" t="n">
         <v>46137</v>
       </c>
     </row>
@@ -2520,10 +2508,10 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O31" s="1" t="n">
         <v>46137</v>
       </c>
     </row>
@@ -2587,10 +2575,10 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O32" s="1" t="n">
         <v>46129</v>
       </c>
     </row>
@@ -2650,10 +2638,10 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O33" s="1" t="n">
         <v>46127</v>
       </c>
     </row>
@@ -2713,10 +2701,10 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O34" s="1" t="n">
         <v>46127</v>
       </c>
     </row>
@@ -2776,10 +2764,10 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O35" s="1" t="n">
         <v>46122</v>
       </c>
     </row>
@@ -2843,10 +2831,10 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O36" s="1" t="n">
         <v>46120</v>
       </c>
     </row>
@@ -2910,10 +2898,10 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O37" s="1" t="n">
         <v>46120</v>
       </c>
     </row>
@@ -2973,10 +2961,10 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O38" s="1" t="n">
         <v>46119</v>
       </c>
     </row>
@@ -3036,10 +3024,10 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O39" s="1" t="n">
         <v>46118</v>
       </c>
     </row>
@@ -3099,10 +3087,10 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O40" s="1" t="n">
         <v>46115</v>
       </c>
     </row>
@@ -3166,10 +3154,10 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O41" s="1" t="n">
         <v>46115</v>
       </c>
     </row>
@@ -3229,10 +3217,10 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O42" s="1" t="n">
         <v>46110</v>
       </c>
     </row>
@@ -3292,10 +3280,10 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O43" s="1" t="n">
         <v>46106</v>
       </c>
     </row>
@@ -3355,10 +3343,10 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O44" s="1" t="n">
         <v>46097</v>
       </c>
     </row>
@@ -3418,10 +3406,10 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O45" s="1" t="n">
         <v>46090</v>
       </c>
     </row>
@@ -3481,10 +3469,10 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O46" s="1" t="n">
         <v>46055</v>
       </c>
     </row>
@@ -3544,10 +3532,10 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O47" s="1" t="n">
         <v>46048</v>
       </c>
     </row>
@@ -3607,10 +3595,10 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O48" s="1" t="n">
         <v>46043</v>
       </c>
     </row>
@@ -3674,10 +3662,10 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O49" s="1" t="n">
         <v>46042</v>
       </c>
     </row>
@@ -3737,10 +3725,10 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O50" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O50" s="1" t="n">
         <v>46037</v>
       </c>
     </row>
@@ -3804,10 +3792,10 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O51" s="1" t="n">
         <v>46032</v>
       </c>
     </row>
@@ -3867,10 +3855,10 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O52" s="1" t="n">
         <v>46022</v>
       </c>
     </row>
@@ -3930,10 +3918,10 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O53" s="1" t="n">
         <v>46021</v>
       </c>
     </row>
@@ -3993,10 +3981,10 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O54" s="1" t="n">
         <v>46016</v>
       </c>
     </row>
@@ -4056,10 +4044,10 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O55" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O55" s="1" t="n">
         <v>46011</v>
       </c>
     </row>
@@ -4119,10 +4107,10 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O56" s="1" t="n">
         <v>46009</v>
       </c>
     </row>
@@ -4182,10 +4170,10 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O57" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O57" s="1" t="n">
         <v>46006</v>
       </c>
     </row>
@@ -4245,10 +4233,10 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O58" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O58" s="1" t="n">
         <v>46005</v>
       </c>
     </row>
@@ -4308,10 +4296,10 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O59" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O59" s="1" t="n">
         <v>46002</v>
       </c>
     </row>
@@ -4375,10 +4363,10 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O60" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O60" s="1" t="n">
         <v>46002</v>
       </c>
     </row>
@@ -4438,10 +4426,10 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O61" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O61" s="1" t="n">
         <v>45999</v>
       </c>
     </row>
@@ -4501,10 +4489,10 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O62" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O62" s="1" t="n">
         <v>45999</v>
       </c>
     </row>
@@ -4568,10 +4556,10 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O63" s="1" t="n">
         <v>45996</v>
       </c>
     </row>
@@ -4631,10 +4619,10 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O64" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O64" s="1" t="n">
         <v>45996</v>
       </c>
     </row>
@@ -4698,10 +4686,10 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O65" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O65" s="1" t="n">
         <v>45995</v>
       </c>
     </row>
@@ -4761,10 +4749,10 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O66" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O66" s="1" t="n">
         <v>45992</v>
       </c>
     </row>
@@ -4824,10 +4812,10 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O67" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O67" s="1" t="n">
         <v>45988</v>
       </c>
     </row>
@@ -4887,10 +4875,10 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O68" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O68" s="1" t="n">
         <v>45972</v>
       </c>
     </row>
@@ -4950,10 +4938,10 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O69" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O69" s="1" t="n">
         <v>45968</v>
       </c>
     </row>
@@ -5013,10 +5001,10 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O70" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O70" s="1" t="n">
         <v>45961</v>
       </c>
     </row>
@@ -5080,10 +5068,10 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O71" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O71" s="1" t="n">
         <v>45961</v>
       </c>
     </row>
@@ -5143,10 +5131,10 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O72" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O72" s="1" t="n">
         <v>45959</v>
       </c>
     </row>
@@ -5206,10 +5194,10 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O73" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O73" s="1" t="n">
         <v>45955</v>
       </c>
     </row>
@@ -5269,10 +5257,10 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O74" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O74" s="1" t="n">
         <v>45955</v>
       </c>
     </row>
@@ -5332,10 +5320,10 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O75" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O75" s="1" t="n">
         <v>45950</v>
       </c>
     </row>
@@ -5395,10 +5383,10 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O76" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O76" s="1" t="n">
         <v>45941</v>
       </c>
     </row>
@@ -5458,10 +5446,10 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O77" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O77" s="1" t="n">
         <v>45940</v>
       </c>
     </row>
@@ -5525,10 +5513,10 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O78" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O78" s="1" t="n">
         <v>45938</v>
       </c>
     </row>
@@ -5588,10 +5576,10 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O79" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O79" s="1" t="n">
         <v>45933</v>
       </c>
     </row>
@@ -5651,10 +5639,10 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O80" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O80" s="1" t="n">
         <v>45932</v>
       </c>
     </row>
@@ -5714,10 +5702,10 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O81" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O81" s="1" t="n">
         <v>45931</v>
       </c>
     </row>
@@ -5777,10 +5765,10 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O82" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O82" s="1" t="n">
         <v>45929</v>
       </c>
     </row>
@@ -5840,10 +5828,10 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O83" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O83" s="1" t="n">
         <v>45925</v>
       </c>
     </row>
@@ -5903,10 +5891,10 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O84" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O84" s="1" t="n">
         <v>45916</v>
       </c>
     </row>
@@ -5966,10 +5954,10 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O85" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O85" s="1" t="n">
         <v>45909</v>
       </c>
     </row>
@@ -6029,10 +6017,10 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O86" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O86" s="1" t="n">
         <v>45894</v>
       </c>
     </row>
@@ -6092,10 +6080,10 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O87" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O87" s="1" t="n">
         <v>45838</v>
       </c>
     </row>
@@ -6155,10 +6143,10 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O88" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O88" s="1" t="n">
         <v>45828</v>
       </c>
     </row>
@@ -6218,10 +6206,10 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O89" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O89" s="1" t="n">
         <v>45826</v>
       </c>
     </row>
@@ -6281,10 +6269,10 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O90" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O90" s="1" t="n">
         <v>45824</v>
       </c>
     </row>
@@ -6344,10 +6332,10 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O91" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O91" s="1" t="n">
         <v>45824</v>
       </c>
     </row>
@@ -6407,10 +6395,10 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O92" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O92" s="1" t="n">
         <v>45812</v>
       </c>
     </row>
@@ -6474,10 +6462,10 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O93" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O93" s="1" t="n">
         <v>45811</v>
       </c>
     </row>
@@ -6537,10 +6525,10 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O94" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O94" s="1" t="n">
         <v>45807</v>
       </c>
     </row>
@@ -6600,10 +6588,10 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O95" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O95" s="1" t="n">
         <v>45804</v>
       </c>
     </row>
@@ -6667,10 +6655,10 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O96" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O96" s="1" t="n">
         <v>45796</v>
       </c>
     </row>
@@ -6730,10 +6718,10 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O97" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O97" s="1" t="n">
         <v>45790</v>
       </c>
     </row>
@@ -6793,10 +6781,10 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O98" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O98" s="1" t="n">
         <v>45784</v>
       </c>
     </row>
@@ -6856,10 +6844,10 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O99" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O99" s="1" t="n">
         <v>45777</v>
       </c>
     </row>
@@ -6923,10 +6911,10 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O100" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O100" s="1" t="n">
         <v>45777</v>
       </c>
     </row>
@@ -6986,10 +6974,10 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O101" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O101" s="1" t="n">
         <v>45776</v>
       </c>
     </row>
@@ -7049,10 +7037,10 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O102" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O102" s="1" t="n">
         <v>45772</v>
       </c>
     </row>
@@ -7112,10 +7100,10 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O103" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O103" s="1" t="n">
         <v>45772</v>
       </c>
     </row>
@@ -7175,10 +7163,10 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O104" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O104" s="1" t="n">
         <v>45772</v>
       </c>
     </row>
@@ -7238,10 +7226,10 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O105" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O105" s="1" t="n">
         <v>45759</v>
       </c>
     </row>
@@ -7301,10 +7289,10 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O106" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O106" s="1" t="n">
         <v>45757</v>
       </c>
     </row>
@@ -7368,10 +7356,10 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O107" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O107" s="1" t="n">
         <v>45756</v>
       </c>
     </row>
@@ -7431,10 +7419,10 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O108" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O108" s="1" t="n">
         <v>45750</v>
       </c>
     </row>
@@ -7494,10 +7482,10 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O109" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O109" s="1" t="n">
         <v>45749</v>
       </c>
     </row>
@@ -7557,10 +7545,10 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O110" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O110" s="1" t="n">
         <v>45748</v>
       </c>
     </row>
@@ -7620,10 +7608,10 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O111" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O111" s="1" t="n">
         <v>45745</v>
       </c>
     </row>
@@ -7683,10 +7671,10 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O112" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O112" s="1" t="n">
         <v>45737</v>
       </c>
     </row>
@@ -7746,10 +7734,10 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O113" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O113" s="1" t="n">
         <v>45725</v>
       </c>
     </row>
@@ -7809,10 +7797,10 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O114" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O114" s="1" t="n">
         <v>45719</v>
       </c>
     </row>
@@ -7872,10 +7860,10 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O115" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O115" s="1" t="n">
         <v>45716</v>
       </c>
     </row>
@@ -7935,10 +7923,10 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O116" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O116" s="1" t="n">
         <v>45672</v>
       </c>
     </row>
@@ -7998,10 +7986,10 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O117" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O117" s="1" t="n">
         <v>45672</v>
       </c>
     </row>
@@ -8061,10 +8049,10 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O118" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O118" s="1" t="n">
         <v>45667</v>
       </c>
     </row>
@@ -8124,10 +8112,10 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O119" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O119" s="1" t="n">
         <v>45657</v>
       </c>
     </row>
@@ -8187,10 +8175,10 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O120" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O120" s="1" t="n">
         <v>45653</v>
       </c>
     </row>
@@ -8250,10 +8238,10 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O121" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O121" s="1" t="n">
         <v>45653</v>
       </c>
     </row>
@@ -8313,10 +8301,10 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O122" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O122" s="1" t="n">
         <v>45653</v>
       </c>
     </row>
@@ -8376,10 +8364,10 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O123" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O123" s="1" t="n">
         <v>45650</v>
       </c>
     </row>
@@ -8439,10 +8427,10 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O124" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O124" s="1" t="n">
         <v>45635</v>
       </c>
     </row>
@@ -8502,10 +8490,10 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O125" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O125" s="1" t="n">
         <v>45632</v>
       </c>
     </row>
@@ -8569,10 +8557,10 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O126" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O126" s="1" t="n">
         <v>45630</v>
       </c>
     </row>
@@ -8632,10 +8620,10 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O127" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O127" s="1" t="n">
         <v>45626</v>
       </c>
     </row>
@@ -8699,10 +8687,10 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O128" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O128" s="1" t="n">
         <v>45615</v>
       </c>
     </row>
@@ -8762,10 +8750,10 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O129" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O129" s="1" t="n">
         <v>45613</v>
       </c>
     </row>
@@ -8825,10 +8813,10 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O130" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O130" s="1" t="n">
         <v>45609</v>
       </c>
     </row>
@@ -8888,10 +8876,10 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O131" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O131" s="1" t="n">
         <v>45595</v>
       </c>
     </row>
@@ -8955,10 +8943,10 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O132" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O132" s="1" t="n">
         <v>45595</v>
       </c>
     </row>
@@ -9018,10 +9006,10 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O133" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O133" s="1" t="n">
         <v>45590</v>
       </c>
     </row>
@@ -9081,10 +9069,10 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O134" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O134" s="1" t="n">
         <v>45590</v>
       </c>
     </row>
@@ -9144,10 +9132,10 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O135" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O135" s="1" t="n">
         <v>45586</v>
       </c>
     </row>
@@ -9207,10 +9195,10 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O136" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O136" s="1" t="n">
         <v>45577</v>
       </c>
     </row>
@@ -9270,10 +9258,10 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O137" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O137" s="1" t="n">
         <v>45566</v>
       </c>
     </row>
@@ -9333,10 +9321,10 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O138" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O138" s="1" t="n">
         <v>45562</v>
       </c>
     </row>
@@ -9396,10 +9384,10 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O139" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O139" s="1" t="n">
         <v>45545</v>
       </c>
     </row>
@@ -9459,10 +9447,10 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O140" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O140" s="1" t="n">
         <v>45532</v>
       </c>
     </row>
@@ -9522,10 +9510,10 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O141" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O141" s="1" t="n">
         <v>45506</v>
       </c>
     </row>
@@ -9585,10 +9573,10 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O142" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O142" s="1" t="n">
         <v>45485</v>
       </c>
     </row>
@@ -9648,10 +9636,10 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O143" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O143" s="1" t="n">
         <v>45483</v>
       </c>
     </row>
@@ -9711,10 +9699,10 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O144" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O144" s="1" t="n">
         <v>45473</v>
       </c>
     </row>
@@ -9774,10 +9762,10 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O145" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O145" s="1" t="n">
         <v>45470</v>
       </c>
     </row>
@@ -9837,10 +9825,10 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O146" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O146" s="1" t="n">
         <v>45469</v>
       </c>
     </row>
@@ -9900,10 +9888,10 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O147" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O147" s="1" t="n">
         <v>45467</v>
       </c>
     </row>
@@ -9963,10 +9951,10 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O148" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O148" s="1" t="n">
         <v>45463</v>
       </c>
     </row>
@@ -10026,10 +10014,10 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O149" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O149" s="1" t="n">
         <v>45446</v>
       </c>
     </row>
@@ -10089,10 +10077,10 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O150" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O150" s="1" t="n">
         <v>45436</v>
       </c>
     </row>
@@ -10152,10 +10140,10 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O151" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O151" s="1" t="n">
         <v>45435</v>
       </c>
     </row>
@@ -10215,10 +10203,10 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O152" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O152" s="1" t="n">
         <v>45429</v>
       </c>
     </row>
@@ -10278,10 +10266,10 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O153" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O153" s="1" t="n">
         <v>45411</v>
       </c>
     </row>
@@ -10341,10 +10329,10 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O154" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O154" s="1" t="n">
         <v>45407</v>
       </c>
     </row>
@@ -10404,10 +10392,10 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O155" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O155" s="1" t="n">
         <v>45394</v>
       </c>
     </row>
@@ -10467,10 +10455,10 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O156" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O156" s="1" t="n">
         <v>45383</v>
       </c>
     </row>
@@ -10530,10 +10518,10 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O157" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O157" s="1" t="n">
         <v>45380</v>
       </c>
     </row>
@@ -10593,10 +10581,10 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O158" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O158" s="1" t="n">
         <v>45350</v>
       </c>
     </row>
@@ -10656,10 +10644,10 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O159" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O159" s="1" t="n">
         <v>45323</v>
       </c>
     </row>
@@ -10719,10 +10707,10 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O160" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O160" s="1" t="n">
         <v>45322</v>
       </c>
     </row>
@@ -10782,10 +10770,10 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O161" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O161" s="1" t="n">
         <v>45306</v>
       </c>
     </row>
@@ -10845,10 +10833,10 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O162" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O162" s="1" t="n">
         <v>45290</v>
       </c>
     </row>
@@ -10908,10 +10896,10 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O163" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O163" s="1" t="n">
         <v>45288</v>
       </c>
     </row>
@@ -10971,10 +10959,10 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O164" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O164" s="1" t="n">
         <v>45268</v>
       </c>
     </row>
@@ -11034,10 +11022,10 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O165" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O165" s="1" t="n">
         <v>45231</v>
       </c>
     </row>
@@ -11097,10 +11085,10 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O166" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O166" s="1" t="n">
         <v>45209</v>
       </c>
     </row>
@@ -11160,10 +11148,10 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O167" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O167" s="1" t="n">
         <v>45205</v>
       </c>
     </row>
@@ -11223,10 +11211,10 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O168" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O168" s="1" t="n">
         <v>45166</v>
       </c>
     </row>
@@ -11286,10 +11274,10 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O169" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O169" s="1" t="n">
         <v>45139</v>
       </c>
     </row>
@@ -11349,10 +11337,10 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O170" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O170" s="1" t="n">
         <v>45138</v>
       </c>
     </row>
@@ -11412,10 +11400,10 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O171" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O171" s="1" t="n">
         <v>45121</v>
       </c>
     </row>
@@ -11475,10 +11463,10 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O172" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O172" s="1" t="n">
         <v>45091</v>
       </c>
     </row>
@@ -11538,10 +11526,10 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O173" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O173" s="1" t="n">
         <v>45086</v>
       </c>
     </row>
@@ -11601,10 +11589,10 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O174" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O174" s="1" t="n">
         <v>45058</v>
       </c>
     </row>
@@ -11664,10 +11652,10 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O175" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O175" s="1" t="n">
         <v>45028</v>
       </c>
     </row>
@@ -11727,10 +11715,10 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O176" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O176" s="1" t="n">
         <v>45016</v>
       </c>
     </row>
@@ -11790,10 +11778,10 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O177" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O177" s="1" t="n">
         <v>45002</v>
       </c>
     </row>
@@ -11853,10 +11841,10 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O178" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O178" s="1" t="n">
         <v>44945</v>
       </c>
     </row>
@@ -11916,10 +11904,10 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O179" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O179" s="1" t="n">
         <v>44899</v>
       </c>
     </row>
@@ -11979,10 +11967,10 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O180" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O180" s="1" t="n">
         <v>44895</v>
       </c>
     </row>
@@ -12042,10 +12030,10 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O181" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O181" s="1" t="n">
         <v>44888</v>
       </c>
     </row>
@@ -12105,10 +12093,10 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O182" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O182" s="1" t="n">
         <v>44886</v>
       </c>
     </row>
@@ -12168,10 +12156,10 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O183" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O183" s="1" t="n">
         <v>44873</v>
       </c>
     </row>
@@ -12231,10 +12219,10 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O184" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O184" s="1" t="n">
         <v>44823</v>
       </c>
     </row>
@@ -12294,10 +12282,10 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O185" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O185" s="1" t="n">
         <v>44740</v>
       </c>
     </row>
@@ -12357,10 +12345,10 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O186" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O186" s="1" t="n">
         <v>44733</v>
       </c>
     </row>
@@ -12420,10 +12408,10 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O187" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O187" s="1" t="n">
         <v>44676</v>
       </c>
     </row>
@@ -12483,10 +12471,10 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O188" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O188" s="1" t="n">
         <v>44671</v>
       </c>
     </row>
@@ -12546,10 +12534,10 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O189" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O189" s="1" t="n">
         <v>44655</v>
       </c>
     </row>
@@ -12609,10 +12597,10 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O190" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O190" s="1" t="n">
         <v>44649</v>
       </c>
     </row>
@@ -12672,10 +12660,10 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O191" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O191" s="1" t="n">
         <v>44587</v>
       </c>
     </row>
@@ -12735,10 +12723,10 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O192" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O192" s="1" t="n">
         <v>44481</v>
       </c>
     </row>
@@ -12798,10 +12786,10 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O193" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O193" s="1" t="n">
         <v>44424</v>
       </c>
     </row>
@@ -12861,10 +12849,10 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:43</t>
-        </is>
-      </c>
-      <c r="O194" s="2" t="n">
+          <t>2026-09-18 07:51:06</t>
+        </is>
+      </c>
+      <c r="O194" s="1" t="n">
         <v>44335</v>
       </c>
     </row>

--- a/pipeline/credit_rating/output/fiinratings_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/fiinratings_xhtn_20260918.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O2" s="1" t="n">
@@ -632,7 +632,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O3" s="1" t="n">
@@ -707,7 +707,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O4" s="1" t="n">
@@ -770,7 +770,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O5" s="1" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O6" s="1" t="n">
@@ -904,7 +904,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O7" s="1" t="n">
@@ -971,7 +971,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O8" s="1" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O9" s="1" t="n">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O10" s="1" t="n">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O11" s="1" t="n">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O12" s="1" t="n">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O13" s="1" t="n">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O14" s="1" t="n">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O15" s="1" t="n">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O16" s="1" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O17" s="1" t="n">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O18" s="1" t="n">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O19" s="1" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O20" s="1" t="n">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O21" s="1" t="n">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O22" s="1" t="n">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O23" s="1" t="n">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O24" s="1" t="n">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O25" s="1" t="n">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O26" s="1" t="n">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O27" s="1" t="n">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O28" s="1" t="n">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O29" s="1" t="n">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O30" s="1" t="n">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O31" s="1" t="n">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O32" s="1" t="n">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O33" s="1" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O34" s="1" t="n">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O35" s="1" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O36" s="1" t="n">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O37" s="1" t="n">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O38" s="1" t="n">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O39" s="1" t="n">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O40" s="1" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O41" s="1" t="n">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O42" s="1" t="n">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O43" s="1" t="n">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O44" s="1" t="n">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O45" s="1" t="n">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O46" s="1" t="n">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O47" s="1" t="n">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O48" s="1" t="n">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O49" s="1" t="n">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O50" s="1" t="n">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O51" s="1" t="n">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O52" s="1" t="n">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O53" s="1" t="n">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O54" s="1" t="n">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O55" s="1" t="n">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O56" s="1" t="n">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O57" s="1" t="n">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O58" s="1" t="n">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O59" s="1" t="n">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O60" s="1" t="n">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O61" s="1" t="n">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O62" s="1" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O63" s="1" t="n">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O64" s="1" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O65" s="1" t="n">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O66" s="1" t="n">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O67" s="1" t="n">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O68" s="1" t="n">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O69" s="1" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O70" s="1" t="n">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O71" s="1" t="n">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O72" s="1" t="n">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O73" s="1" t="n">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O74" s="1" t="n">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O75" s="1" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O76" s="1" t="n">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O77" s="1" t="n">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O78" s="1" t="n">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O79" s="1" t="n">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O80" s="1" t="n">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O81" s="1" t="n">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O82" s="1" t="n">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O83" s="1" t="n">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O84" s="1" t="n">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O85" s="1" t="n">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O86" s="1" t="n">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O87" s="1" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O88" s="1" t="n">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O89" s="1" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O90" s="1" t="n">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O91" s="1" t="n">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O92" s="1" t="n">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O93" s="1" t="n">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O94" s="1" t="n">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O95" s="1" t="n">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O96" s="1" t="n">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O97" s="1" t="n">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O98" s="1" t="n">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O99" s="1" t="n">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O100" s="1" t="n">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O101" s="1" t="n">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O102" s="1" t="n">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O103" s="1" t="n">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O104" s="1" t="n">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O105" s="1" t="n">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O106" s="1" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O107" s="1" t="n">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O108" s="1" t="n">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O109" s="1" t="n">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O110" s="1" t="n">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O111" s="1" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O112" s="1" t="n">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O113" s="1" t="n">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O114" s="1" t="n">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O115" s="1" t="n">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O116" s="1" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O117" s="1" t="n">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O118" s="1" t="n">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O119" s="1" t="n">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O120" s="1" t="n">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O121" s="1" t="n">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O122" s="1" t="n">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O123" s="1" t="n">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O124" s="1" t="n">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O125" s="1" t="n">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O126" s="1" t="n">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O127" s="1" t="n">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O128" s="1" t="n">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O129" s="1" t="n">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O130" s="1" t="n">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O131" s="1" t="n">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O132" s="1" t="n">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O133" s="1" t="n">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O134" s="1" t="n">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O135" s="1" t="n">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O136" s="1" t="n">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O137" s="1" t="n">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O138" s="1" t="n">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O139" s="1" t="n">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O140" s="1" t="n">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O141" s="1" t="n">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O142" s="1" t="n">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O143" s="1" t="n">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O144" s="1" t="n">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O145" s="1" t="n">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O146" s="1" t="n">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O147" s="1" t="n">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O148" s="1" t="n">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O149" s="1" t="n">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O150" s="1" t="n">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O151" s="1" t="n">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O152" s="1" t="n">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O153" s="1" t="n">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O154" s="1" t="n">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O155" s="1" t="n">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O156" s="1" t="n">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O157" s="1" t="n">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O158" s="1" t="n">
@@ -10644,7 +10644,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O159" s="1" t="n">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O160" s="1" t="n">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O161" s="1" t="n">
@@ -10833,7 +10833,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O162" s="1" t="n">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O163" s="1" t="n">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O164" s="1" t="n">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O165" s="1" t="n">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O166" s="1" t="n">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O167" s="1" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O168" s="1" t="n">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O169" s="1" t="n">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O170" s="1" t="n">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O171" s="1" t="n">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O172" s="1" t="n">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O173" s="1" t="n">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O174" s="1" t="n">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O175" s="1" t="n">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O176" s="1" t="n">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O177" s="1" t="n">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O178" s="1" t="n">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O179" s="1" t="n">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O180" s="1" t="n">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O181" s="1" t="n">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O182" s="1" t="n">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O183" s="1" t="n">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O184" s="1" t="n">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O185" s="1" t="n">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O186" s="1" t="n">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O187" s="1" t="n">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O188" s="1" t="n">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O189" s="1" t="n">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O190" s="1" t="n">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O191" s="1" t="n">
@@ -12723,7 +12723,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O192" s="1" t="n">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O193" s="1" t="n">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="O194" s="1" t="n">

--- a/pipeline/credit_rating/output/fiinratings_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/fiinratings_xhtn_20260918.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O2" s="1" t="n">
@@ -632,7 +632,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O3" s="1" t="n">
@@ -707,7 +707,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O4" s="1" t="n">
@@ -770,7 +770,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O5" s="1" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O6" s="1" t="n">
@@ -904,7 +904,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O7" s="1" t="n">
@@ -971,7 +971,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O8" s="1" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O9" s="1" t="n">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O10" s="1" t="n">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O11" s="1" t="n">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O12" s="1" t="n">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O13" s="1" t="n">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O14" s="1" t="n">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O15" s="1" t="n">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O16" s="1" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O17" s="1" t="n">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O18" s="1" t="n">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O19" s="1" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O20" s="1" t="n">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O21" s="1" t="n">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O22" s="1" t="n">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O23" s="1" t="n">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O24" s="1" t="n">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O25" s="1" t="n">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O26" s="1" t="n">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O27" s="1" t="n">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O28" s="1" t="n">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O29" s="1" t="n">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O30" s="1" t="n">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O31" s="1" t="n">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O32" s="1" t="n">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O33" s="1" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O34" s="1" t="n">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O35" s="1" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O36" s="1" t="n">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O37" s="1" t="n">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O38" s="1" t="n">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O39" s="1" t="n">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O40" s="1" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O41" s="1" t="n">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O42" s="1" t="n">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O43" s="1" t="n">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O44" s="1" t="n">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O45" s="1" t="n">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O46" s="1" t="n">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O47" s="1" t="n">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O48" s="1" t="n">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O49" s="1" t="n">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O50" s="1" t="n">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O51" s="1" t="n">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O52" s="1" t="n">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O53" s="1" t="n">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O54" s="1" t="n">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O55" s="1" t="n">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O56" s="1" t="n">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O57" s="1" t="n">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O58" s="1" t="n">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O59" s="1" t="n">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O60" s="1" t="n">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O61" s="1" t="n">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O62" s="1" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O63" s="1" t="n">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O64" s="1" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O65" s="1" t="n">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O66" s="1" t="n">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O67" s="1" t="n">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O68" s="1" t="n">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O69" s="1" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O70" s="1" t="n">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O71" s="1" t="n">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O72" s="1" t="n">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O73" s="1" t="n">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O74" s="1" t="n">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O75" s="1" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O76" s="1" t="n">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O77" s="1" t="n">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O78" s="1" t="n">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O79" s="1" t="n">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O80" s="1" t="n">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O81" s="1" t="n">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O82" s="1" t="n">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O83" s="1" t="n">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O84" s="1" t="n">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O85" s="1" t="n">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O86" s="1" t="n">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O87" s="1" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O88" s="1" t="n">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O89" s="1" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O90" s="1" t="n">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O91" s="1" t="n">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O92" s="1" t="n">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O93" s="1" t="n">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O94" s="1" t="n">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O95" s="1" t="n">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O96" s="1" t="n">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O97" s="1" t="n">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O98" s="1" t="n">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O99" s="1" t="n">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O100" s="1" t="n">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O101" s="1" t="n">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O102" s="1" t="n">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O103" s="1" t="n">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O104" s="1" t="n">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O105" s="1" t="n">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O106" s="1" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O107" s="1" t="n">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O108" s="1" t="n">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O109" s="1" t="n">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O110" s="1" t="n">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O111" s="1" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O112" s="1" t="n">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O113" s="1" t="n">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O114" s="1" t="n">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O115" s="1" t="n">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O116" s="1" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O117" s="1" t="n">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O118" s="1" t="n">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O119" s="1" t="n">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O120" s="1" t="n">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O121" s="1" t="n">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O122" s="1" t="n">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O123" s="1" t="n">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O124" s="1" t="n">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O125" s="1" t="n">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O126" s="1" t="n">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O127" s="1" t="n">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O128" s="1" t="n">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O129" s="1" t="n">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O130" s="1" t="n">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O131" s="1" t="n">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O132" s="1" t="n">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O133" s="1" t="n">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O134" s="1" t="n">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O135" s="1" t="n">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O136" s="1" t="n">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O137" s="1" t="n">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O138" s="1" t="n">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O139" s="1" t="n">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O140" s="1" t="n">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O141" s="1" t="n">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O142" s="1" t="n">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O143" s="1" t="n">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O144" s="1" t="n">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O145" s="1" t="n">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O146" s="1" t="n">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O147" s="1" t="n">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O148" s="1" t="n">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O149" s="1" t="n">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O150" s="1" t="n">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O151" s="1" t="n">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O152" s="1" t="n">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O153" s="1" t="n">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O154" s="1" t="n">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O155" s="1" t="n">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O156" s="1" t="n">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O157" s="1" t="n">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O158" s="1" t="n">
@@ -10644,7 +10644,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O159" s="1" t="n">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O160" s="1" t="n">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O161" s="1" t="n">
@@ -10833,7 +10833,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O162" s="1" t="n">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O163" s="1" t="n">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O164" s="1" t="n">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O165" s="1" t="n">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O166" s="1" t="n">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O167" s="1" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O168" s="1" t="n">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O169" s="1" t="n">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O170" s="1" t="n">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O171" s="1" t="n">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O172" s="1" t="n">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O173" s="1" t="n">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O174" s="1" t="n">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O175" s="1" t="n">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O176" s="1" t="n">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O177" s="1" t="n">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O178" s="1" t="n">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O179" s="1" t="n">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O180" s="1" t="n">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O181" s="1" t="n">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O182" s="1" t="n">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O183" s="1" t="n">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O184" s="1" t="n">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O185" s="1" t="n">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O186" s="1" t="n">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O187" s="1" t="n">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O188" s="1" t="n">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O189" s="1" t="n">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O190" s="1" t="n">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O191" s="1" t="n">
@@ -12723,7 +12723,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O192" s="1" t="n">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O193" s="1" t="n">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="O194" s="1" t="n">

--- a/pipeline/credit_rating/output/fiinratings_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/fiinratings_xhtn_20260918.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O2" s="1" t="n">
@@ -632,7 +632,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O3" s="1" t="n">
@@ -707,7 +707,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O4" s="1" t="n">
@@ -770,7 +770,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O5" s="1" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O6" s="1" t="n">
@@ -904,7 +904,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O7" s="1" t="n">
@@ -971,7 +971,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O8" s="1" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O9" s="1" t="n">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O10" s="1" t="n">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O11" s="1" t="n">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O12" s="1" t="n">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O13" s="1" t="n">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O14" s="1" t="n">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O15" s="1" t="n">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O16" s="1" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O17" s="1" t="n">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O18" s="1" t="n">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O19" s="1" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O20" s="1" t="n">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O21" s="1" t="n">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O22" s="1" t="n">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O23" s="1" t="n">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O24" s="1" t="n">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O25" s="1" t="n">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O26" s="1" t="n">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O27" s="1" t="n">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O28" s="1" t="n">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O29" s="1" t="n">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O30" s="1" t="n">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O31" s="1" t="n">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O32" s="1" t="n">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O33" s="1" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O34" s="1" t="n">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O35" s="1" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O36" s="1" t="n">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O37" s="1" t="n">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O38" s="1" t="n">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O39" s="1" t="n">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O40" s="1" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O41" s="1" t="n">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O42" s="1" t="n">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O43" s="1" t="n">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O44" s="1" t="n">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O45" s="1" t="n">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O46" s="1" t="n">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O47" s="1" t="n">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O48" s="1" t="n">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O49" s="1" t="n">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O50" s="1" t="n">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O51" s="1" t="n">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O52" s="1" t="n">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O53" s="1" t="n">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O54" s="1" t="n">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O55" s="1" t="n">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O56" s="1" t="n">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O57" s="1" t="n">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O58" s="1" t="n">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O59" s="1" t="n">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O60" s="1" t="n">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O61" s="1" t="n">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O62" s="1" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O63" s="1" t="n">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O64" s="1" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O65" s="1" t="n">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O66" s="1" t="n">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O67" s="1" t="n">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O68" s="1" t="n">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O69" s="1" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O70" s="1" t="n">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O71" s="1" t="n">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O72" s="1" t="n">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O73" s="1" t="n">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O74" s="1" t="n">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O75" s="1" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O76" s="1" t="n">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O77" s="1" t="n">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O78" s="1" t="n">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O79" s="1" t="n">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O80" s="1" t="n">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O81" s="1" t="n">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O82" s="1" t="n">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O83" s="1" t="n">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O84" s="1" t="n">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O85" s="1" t="n">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O86" s="1" t="n">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O87" s="1" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O88" s="1" t="n">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O89" s="1" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O90" s="1" t="n">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O91" s="1" t="n">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O92" s="1" t="n">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O93" s="1" t="n">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O94" s="1" t="n">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O95" s="1" t="n">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O96" s="1" t="n">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O97" s="1" t="n">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O98" s="1" t="n">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O99" s="1" t="n">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O100" s="1" t="n">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O101" s="1" t="n">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O102" s="1" t="n">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O103" s="1" t="n">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O104" s="1" t="n">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O105" s="1" t="n">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O106" s="1" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O107" s="1" t="n">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O108" s="1" t="n">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O109" s="1" t="n">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O110" s="1" t="n">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O111" s="1" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O112" s="1" t="n">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O113" s="1" t="n">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O114" s="1" t="n">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O115" s="1" t="n">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O116" s="1" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O117" s="1" t="n">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O118" s="1" t="n">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O119" s="1" t="n">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O120" s="1" t="n">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O121" s="1" t="n">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O122" s="1" t="n">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O123" s="1" t="n">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O124" s="1" t="n">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O125" s="1" t="n">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O126" s="1" t="n">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O127" s="1" t="n">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O128" s="1" t="n">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O129" s="1" t="n">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O130" s="1" t="n">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O131" s="1" t="n">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O132" s="1" t="n">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O133" s="1" t="n">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O134" s="1" t="n">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O135" s="1" t="n">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O136" s="1" t="n">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O137" s="1" t="n">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O138" s="1" t="n">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O139" s="1" t="n">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O140" s="1" t="n">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O141" s="1" t="n">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O142" s="1" t="n">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O143" s="1" t="n">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O144" s="1" t="n">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O145" s="1" t="n">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O146" s="1" t="n">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O147" s="1" t="n">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O148" s="1" t="n">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O149" s="1" t="n">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O150" s="1" t="n">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O151" s="1" t="n">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O152" s="1" t="n">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O153" s="1" t="n">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O154" s="1" t="n">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O155" s="1" t="n">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O156" s="1" t="n">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O157" s="1" t="n">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O158" s="1" t="n">
@@ -10644,7 +10644,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O159" s="1" t="n">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O160" s="1" t="n">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O161" s="1" t="n">
@@ -10833,7 +10833,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O162" s="1" t="n">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O163" s="1" t="n">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O164" s="1" t="n">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O165" s="1" t="n">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O166" s="1" t="n">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O167" s="1" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O168" s="1" t="n">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O169" s="1" t="n">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O170" s="1" t="n">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O171" s="1" t="n">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O172" s="1" t="n">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O173" s="1" t="n">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O174" s="1" t="n">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O175" s="1" t="n">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O176" s="1" t="n">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O177" s="1" t="n">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O178" s="1" t="n">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O179" s="1" t="n">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O180" s="1" t="n">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O181" s="1" t="n">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O182" s="1" t="n">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O183" s="1" t="n">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O184" s="1" t="n">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O185" s="1" t="n">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O186" s="1" t="n">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O187" s="1" t="n">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O188" s="1" t="n">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O189" s="1" t="n">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O190" s="1" t="n">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O191" s="1" t="n">
@@ -12723,7 +12723,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O192" s="1" t="n">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O193" s="1" t="n">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="O194" s="1" t="n">

--- a/pipeline/credit_rating/output/fiinratings_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/fiinratings_xhtn_20260918.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O2" s="1" t="n">
@@ -632,7 +632,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O3" s="1" t="n">
@@ -707,7 +707,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O4" s="1" t="n">
@@ -770,7 +770,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O5" s="1" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O6" s="1" t="n">
@@ -904,7 +904,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O7" s="1" t="n">
@@ -971,7 +971,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O8" s="1" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O9" s="1" t="n">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O10" s="1" t="n">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O11" s="1" t="n">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O12" s="1" t="n">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O13" s="1" t="n">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O14" s="1" t="n">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O15" s="1" t="n">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O16" s="1" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O17" s="1" t="n">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O18" s="1" t="n">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O19" s="1" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O20" s="1" t="n">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O21" s="1" t="n">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O22" s="1" t="n">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O23" s="1" t="n">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O24" s="1" t="n">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O25" s="1" t="n">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O26" s="1" t="n">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O27" s="1" t="n">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O28" s="1" t="n">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O29" s="1" t="n">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O30" s="1" t="n">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O31" s="1" t="n">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O32" s="1" t="n">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O33" s="1" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O34" s="1" t="n">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O35" s="1" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O36" s="1" t="n">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O37" s="1" t="n">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O38" s="1" t="n">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O39" s="1" t="n">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O40" s="1" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O41" s="1" t="n">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O42" s="1" t="n">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O43" s="1" t="n">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O44" s="1" t="n">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O45" s="1" t="n">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O46" s="1" t="n">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O47" s="1" t="n">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O48" s="1" t="n">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O49" s="1" t="n">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O50" s="1" t="n">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O51" s="1" t="n">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O52" s="1" t="n">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O53" s="1" t="n">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O54" s="1" t="n">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O55" s="1" t="n">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O56" s="1" t="n">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O57" s="1" t="n">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O58" s="1" t="n">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O59" s="1" t="n">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O60" s="1" t="n">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O61" s="1" t="n">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O62" s="1" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O63" s="1" t="n">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O64" s="1" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O65" s="1" t="n">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O66" s="1" t="n">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O67" s="1" t="n">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O68" s="1" t="n">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O69" s="1" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O70" s="1" t="n">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O71" s="1" t="n">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O72" s="1" t="n">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O73" s="1" t="n">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O74" s="1" t="n">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O75" s="1" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O76" s="1" t="n">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O77" s="1" t="n">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O78" s="1" t="n">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O79" s="1" t="n">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O80" s="1" t="n">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O81" s="1" t="n">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O82" s="1" t="n">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O83" s="1" t="n">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O84" s="1" t="n">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O85" s="1" t="n">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O86" s="1" t="n">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O87" s="1" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O88" s="1" t="n">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O89" s="1" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O90" s="1" t="n">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O91" s="1" t="n">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O92" s="1" t="n">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O93" s="1" t="n">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O94" s="1" t="n">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O95" s="1" t="n">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O96" s="1" t="n">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O97" s="1" t="n">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O98" s="1" t="n">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O99" s="1" t="n">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O100" s="1" t="n">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O101" s="1" t="n">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O102" s="1" t="n">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O103" s="1" t="n">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O104" s="1" t="n">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O105" s="1" t="n">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O106" s="1" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O107" s="1" t="n">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O108" s="1" t="n">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O109" s="1" t="n">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O110" s="1" t="n">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O111" s="1" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O112" s="1" t="n">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O113" s="1" t="n">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O114" s="1" t="n">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O115" s="1" t="n">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O116" s="1" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O117" s="1" t="n">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O118" s="1" t="n">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O119" s="1" t="n">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O120" s="1" t="n">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O121" s="1" t="n">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O122" s="1" t="n">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O123" s="1" t="n">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O124" s="1" t="n">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O125" s="1" t="n">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O126" s="1" t="n">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O127" s="1" t="n">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O128" s="1" t="n">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O129" s="1" t="n">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O130" s="1" t="n">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O131" s="1" t="n">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O132" s="1" t="n">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O133" s="1" t="n">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O134" s="1" t="n">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O135" s="1" t="n">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O136" s="1" t="n">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O137" s="1" t="n">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O138" s="1" t="n">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O139" s="1" t="n">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O140" s="1" t="n">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O141" s="1" t="n">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O142" s="1" t="n">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O143" s="1" t="n">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O144" s="1" t="n">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O145" s="1" t="n">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O146" s="1" t="n">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O147" s="1" t="n">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O148" s="1" t="n">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O149" s="1" t="n">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O150" s="1" t="n">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O151" s="1" t="n">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O152" s="1" t="n">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O153" s="1" t="n">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O154" s="1" t="n">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O155" s="1" t="n">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O156" s="1" t="n">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O157" s="1" t="n">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O158" s="1" t="n">
@@ -10644,7 +10644,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O159" s="1" t="n">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O160" s="1" t="n">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O161" s="1" t="n">
@@ -10833,7 +10833,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O162" s="1" t="n">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O163" s="1" t="n">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O164" s="1" t="n">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O165" s="1" t="n">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O166" s="1" t="n">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O167" s="1" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O168" s="1" t="n">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O169" s="1" t="n">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O170" s="1" t="n">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O171" s="1" t="n">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O172" s="1" t="n">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O173" s="1" t="n">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O174" s="1" t="n">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O175" s="1" t="n">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O176" s="1" t="n">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O177" s="1" t="n">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O178" s="1" t="n">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O179" s="1" t="n">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O180" s="1" t="n">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O181" s="1" t="n">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O182" s="1" t="n">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O183" s="1" t="n">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O184" s="1" t="n">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O185" s="1" t="n">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O186" s="1" t="n">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O187" s="1" t="n">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O188" s="1" t="n">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O189" s="1" t="n">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O190" s="1" t="n">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O191" s="1" t="n">
@@ -12723,7 +12723,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O192" s="1" t="n">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O193" s="1" t="n">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="O194" s="1" t="n">

--- a/pipeline/credit_rating/output/fiinratings_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/fiinratings_xhtn_20260918.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O2" s="1" t="n">
@@ -632,7 +632,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O3" s="1" t="n">
@@ -707,7 +707,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O4" s="1" t="n">
@@ -770,7 +770,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O5" s="1" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O6" s="1" t="n">
@@ -904,7 +904,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O7" s="1" t="n">
@@ -971,7 +971,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O8" s="1" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O9" s="1" t="n">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O10" s="1" t="n">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O11" s="1" t="n">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O12" s="1" t="n">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O13" s="1" t="n">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O14" s="1" t="n">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O15" s="1" t="n">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O16" s="1" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O17" s="1" t="n">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O18" s="1" t="n">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O19" s="1" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O20" s="1" t="n">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O21" s="1" t="n">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O22" s="1" t="n">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O23" s="1" t="n">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O24" s="1" t="n">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O25" s="1" t="n">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O26" s="1" t="n">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O27" s="1" t="n">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O28" s="1" t="n">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O29" s="1" t="n">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O30" s="1" t="n">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O31" s="1" t="n">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O32" s="1" t="n">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O33" s="1" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O34" s="1" t="n">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O35" s="1" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O36" s="1" t="n">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O37" s="1" t="n">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O38" s="1" t="n">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O39" s="1" t="n">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O40" s="1" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O41" s="1" t="n">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O42" s="1" t="n">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O43" s="1" t="n">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O44" s="1" t="n">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O45" s="1" t="n">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O46" s="1" t="n">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O47" s="1" t="n">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O48" s="1" t="n">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O49" s="1" t="n">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O50" s="1" t="n">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O51" s="1" t="n">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O52" s="1" t="n">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O53" s="1" t="n">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O54" s="1" t="n">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O55" s="1" t="n">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O56" s="1" t="n">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O57" s="1" t="n">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O58" s="1" t="n">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O59" s="1" t="n">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O60" s="1" t="n">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O61" s="1" t="n">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O62" s="1" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O63" s="1" t="n">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O64" s="1" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O65" s="1" t="n">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O66" s="1" t="n">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O67" s="1" t="n">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O68" s="1" t="n">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O69" s="1" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O70" s="1" t="n">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O71" s="1" t="n">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O72" s="1" t="n">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O73" s="1" t="n">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O74" s="1" t="n">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O75" s="1" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O76" s="1" t="n">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O77" s="1" t="n">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O78" s="1" t="n">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O79" s="1" t="n">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O80" s="1" t="n">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O81" s="1" t="n">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O82" s="1" t="n">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O83" s="1" t="n">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O84" s="1" t="n">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O85" s="1" t="n">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O86" s="1" t="n">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O87" s="1" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O88" s="1" t="n">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O89" s="1" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O90" s="1" t="n">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O91" s="1" t="n">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O92" s="1" t="n">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O93" s="1" t="n">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O94" s="1" t="n">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O95" s="1" t="n">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O96" s="1" t="n">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O97" s="1" t="n">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O98" s="1" t="n">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O99" s="1" t="n">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O100" s="1" t="n">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O101" s="1" t="n">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O102" s="1" t="n">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O103" s="1" t="n">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O104" s="1" t="n">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O105" s="1" t="n">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O106" s="1" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O107" s="1" t="n">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O108" s="1" t="n">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O109" s="1" t="n">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O110" s="1" t="n">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O111" s="1" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O112" s="1" t="n">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O113" s="1" t="n">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O114" s="1" t="n">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O115" s="1" t="n">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O116" s="1" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O117" s="1" t="n">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O118" s="1" t="n">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O119" s="1" t="n">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O120" s="1" t="n">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O121" s="1" t="n">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O122" s="1" t="n">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O123" s="1" t="n">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O124" s="1" t="n">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O125" s="1" t="n">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O126" s="1" t="n">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O127" s="1" t="n">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O128" s="1" t="n">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O129" s="1" t="n">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O130" s="1" t="n">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O131" s="1" t="n">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O132" s="1" t="n">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O133" s="1" t="n">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O134" s="1" t="n">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O135" s="1" t="n">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O136" s="1" t="n">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O137" s="1" t="n">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O138" s="1" t="n">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O139" s="1" t="n">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O140" s="1" t="n">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O141" s="1" t="n">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O142" s="1" t="n">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O143" s="1" t="n">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O144" s="1" t="n">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O145" s="1" t="n">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O146" s="1" t="n">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O147" s="1" t="n">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O148" s="1" t="n">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O149" s="1" t="n">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O150" s="1" t="n">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O151" s="1" t="n">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O152" s="1" t="n">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O153" s="1" t="n">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O154" s="1" t="n">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O155" s="1" t="n">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O156" s="1" t="n">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O157" s="1" t="n">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O158" s="1" t="n">
@@ -10644,7 +10644,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O159" s="1" t="n">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O160" s="1" t="n">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O161" s="1" t="n">
@@ -10833,7 +10833,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O162" s="1" t="n">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O163" s="1" t="n">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O164" s="1" t="n">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O165" s="1" t="n">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O166" s="1" t="n">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O167" s="1" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O168" s="1" t="n">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O169" s="1" t="n">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O170" s="1" t="n">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O171" s="1" t="n">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O172" s="1" t="n">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O173" s="1" t="n">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O174" s="1" t="n">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O175" s="1" t="n">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O176" s="1" t="n">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O177" s="1" t="n">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O178" s="1" t="n">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O179" s="1" t="n">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O180" s="1" t="n">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O181" s="1" t="n">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O182" s="1" t="n">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O183" s="1" t="n">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O184" s="1" t="n">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O185" s="1" t="n">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O186" s="1" t="n">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O187" s="1" t="n">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O188" s="1" t="n">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O189" s="1" t="n">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O190" s="1" t="n">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O191" s="1" t="n">
@@ -12723,7 +12723,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O192" s="1" t="n">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O193" s="1" t="n">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="O194" s="1" t="n">

--- a/pipeline/credit_rating/output/fiinratings_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/fiinratings_xhtn_20260918.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O2" s="1" t="n">
@@ -632,7 +632,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O3" s="1" t="n">
@@ -707,7 +707,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O4" s="1" t="n">
@@ -770,7 +770,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O5" s="1" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O6" s="1" t="n">
@@ -904,7 +904,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O7" s="1" t="n">
@@ -971,7 +971,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O8" s="1" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O9" s="1" t="n">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O10" s="1" t="n">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O11" s="1" t="n">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O12" s="1" t="n">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O13" s="1" t="n">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O14" s="1" t="n">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O15" s="1" t="n">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O16" s="1" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O17" s="1" t="n">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O18" s="1" t="n">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O19" s="1" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O20" s="1" t="n">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O21" s="1" t="n">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O22" s="1" t="n">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O23" s="1" t="n">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O24" s="1" t="n">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O25" s="1" t="n">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O26" s="1" t="n">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O27" s="1" t="n">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O28" s="1" t="n">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O29" s="1" t="n">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O30" s="1" t="n">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O31" s="1" t="n">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O32" s="1" t="n">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O33" s="1" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O34" s="1" t="n">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O35" s="1" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O36" s="1" t="n">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O37" s="1" t="n">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O38" s="1" t="n">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O39" s="1" t="n">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O40" s="1" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O41" s="1" t="n">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O42" s="1" t="n">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O43" s="1" t="n">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O44" s="1" t="n">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O45" s="1" t="n">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O46" s="1" t="n">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O47" s="1" t="n">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O48" s="1" t="n">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O49" s="1" t="n">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O50" s="1" t="n">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O51" s="1" t="n">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O52" s="1" t="n">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O53" s="1" t="n">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O54" s="1" t="n">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O55" s="1" t="n">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O56" s="1" t="n">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O57" s="1" t="n">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O58" s="1" t="n">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O59" s="1" t="n">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O60" s="1" t="n">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O61" s="1" t="n">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O62" s="1" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O63" s="1" t="n">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O64" s="1" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O65" s="1" t="n">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O66" s="1" t="n">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O67" s="1" t="n">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O68" s="1" t="n">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O69" s="1" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O70" s="1" t="n">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O71" s="1" t="n">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O72" s="1" t="n">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O73" s="1" t="n">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O74" s="1" t="n">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O75" s="1" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O76" s="1" t="n">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O77" s="1" t="n">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O78" s="1" t="n">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O79" s="1" t="n">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O80" s="1" t="n">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O81" s="1" t="n">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O82" s="1" t="n">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O83" s="1" t="n">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O84" s="1" t="n">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O85" s="1" t="n">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O86" s="1" t="n">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O87" s="1" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O88" s="1" t="n">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O89" s="1" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O90" s="1" t="n">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O91" s="1" t="n">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O92" s="1" t="n">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O93" s="1" t="n">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O94" s="1" t="n">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O95" s="1" t="n">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O96" s="1" t="n">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O97" s="1" t="n">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O98" s="1" t="n">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O99" s="1" t="n">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O100" s="1" t="n">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O101" s="1" t="n">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O102" s="1" t="n">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O103" s="1" t="n">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O104" s="1" t="n">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O105" s="1" t="n">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O106" s="1" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O107" s="1" t="n">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O108" s="1" t="n">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O109" s="1" t="n">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O110" s="1" t="n">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O111" s="1" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O112" s="1" t="n">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O113" s="1" t="n">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O114" s="1" t="n">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O115" s="1" t="n">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O116" s="1" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O117" s="1" t="n">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O118" s="1" t="n">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O119" s="1" t="n">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O120" s="1" t="n">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O121" s="1" t="n">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O122" s="1" t="n">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O123" s="1" t="n">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O124" s="1" t="n">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O125" s="1" t="n">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O126" s="1" t="n">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O127" s="1" t="n">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O128" s="1" t="n">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O129" s="1" t="n">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O130" s="1" t="n">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O131" s="1" t="n">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O132" s="1" t="n">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O133" s="1" t="n">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O134" s="1" t="n">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O135" s="1" t="n">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O136" s="1" t="n">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O137" s="1" t="n">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O138" s="1" t="n">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O139" s="1" t="n">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O140" s="1" t="n">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O141" s="1" t="n">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O142" s="1" t="n">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O143" s="1" t="n">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O144" s="1" t="n">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O145" s="1" t="n">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O146" s="1" t="n">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O147" s="1" t="n">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O148" s="1" t="n">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O149" s="1" t="n">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O150" s="1" t="n">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O151" s="1" t="n">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O152" s="1" t="n">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O153" s="1" t="n">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O154" s="1" t="n">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O155" s="1" t="n">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O156" s="1" t="n">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O157" s="1" t="n">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O158" s="1" t="n">
@@ -10644,7 +10644,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O159" s="1" t="n">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O160" s="1" t="n">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O161" s="1" t="n">
@@ -10833,7 +10833,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O162" s="1" t="n">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O163" s="1" t="n">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O164" s="1" t="n">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O165" s="1" t="n">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O166" s="1" t="n">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O167" s="1" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O168" s="1" t="n">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O169" s="1" t="n">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O170" s="1" t="n">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O171" s="1" t="n">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O172" s="1" t="n">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O173" s="1" t="n">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O174" s="1" t="n">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O175" s="1" t="n">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O176" s="1" t="n">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O177" s="1" t="n">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O178" s="1" t="n">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O179" s="1" t="n">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O180" s="1" t="n">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O181" s="1" t="n">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O182" s="1" t="n">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O183" s="1" t="n">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O184" s="1" t="n">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O185" s="1" t="n">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O186" s="1" t="n">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O187" s="1" t="n">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O188" s="1" t="n">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O189" s="1" t="n">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O190" s="1" t="n">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O191" s="1" t="n">
@@ -12723,7 +12723,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O192" s="1" t="n">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O193" s="1" t="n">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="O194" s="1" t="n">
